--- a/data/case-study-designing-and-analyzing-a-survey--survey.xlsx
+++ b/data/case-study-designing-and-analyzing-a-survey--survey.xlsx
@@ -30845,7 +30845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Simulated survey for a stratified-sampling + estimation capstone (Chapter 136).</t>
+          <t>Simulated survey for a stratified-sampling + estimation capstone (Chapter 70).</t>
         </is>
       </c>
     </row>
@@ -30866,7 +30866,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Response is roughly uniform across districts (~76%); a small nonresponse-sensitivity check is left for the Take It Further notebook.</t>
+          <t>Response is roughly uniform across districts (~78%); a small nonresponse-sensitivity check is left for the Take It Further notebook.</t>
         </is>
       </c>
     </row>
